--- a/95 Файлы/Допуск. Воскресенская/Допуск. Воскресенская.Монтажлифтсервис.xlsx
+++ b/95 Файлы/Допуск. Воскресенская/Допуск. Воскресенская.Монтажлифтсервис.xlsx
@@ -227,7 +227,7 @@
     <t>Краснодарский край,г.Сочи, ул.Фадеева д.5, кв.31</t>
   </si>
   <si>
-    <t>с 1.04.2026 по 30.04.2026</t>
+    <t>с 1.05.2026 по 31.05.2026</t>
   </si>
 </sst>
 </file>
@@ -505,6 +505,48 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -528,12 +570,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
     </xf>
@@ -545,42 +581,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -880,138 +880,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="47"/>
     </row>
     <row r="2" spans="2:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="35"/>
+      <c r="C2" s="27"/>
       <c r="D2" s="17"/>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="37"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="27"/>
+      <c r="C3" s="41"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="30"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="44"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="41"/>
       <c r="D4" s="11"/>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="30"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="44"/>
     </row>
     <row r="5" spans="2:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="41"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="39"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="51"/>
     </row>
     <row r="6" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="35"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="12"/>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="41"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="29"/>
     </row>
     <row r="7" spans="2:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="35"/>
+      <c r="C7" s="27"/>
       <c r="D7" s="11"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="45"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="33"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="13"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
-      <c r="E8" s="46" t="s">
+      <c r="E8" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="47"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="35"/>
     </row>
     <row r="9" spans="2:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="50"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="38"/>
     </row>
     <row r="10" spans="2:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
@@ -1020,10 +1020,10 @@
       <c r="C10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="51"/>
+      <c r="E10" s="39"/>
       <c r="F10" s="6" t="s">
         <v>10</v>
       </c>
@@ -1036,10 +1036,10 @@
       <c r="I10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="51" t="s">
+      <c r="J10" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="K10" s="51"/>
+      <c r="K10" s="39"/>
     </row>
     <row r="11" spans="2:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
@@ -1216,14 +1216,14 @@
       <c r="K17" s="23"/>
     </row>
     <row r="18" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
       <c r="H18" s="4"/>
       <c r="I18" s="22" t="s">
         <v>46</v>
@@ -1232,12 +1232,12 @@
       <c r="K18" s="24"/>
     </row>
     <row r="19" spans="2:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -1249,7 +1249,7 @@
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="2">
         <f ca="1">TODAY()</f>
-        <v>46112</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
@@ -1259,6 +1259,15 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E4:K4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:K2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:K3"/>
+    <mergeCell ref="E5:K5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="E6:K6"/>
     <mergeCell ref="B19:E19"/>
@@ -1269,15 +1278,6 @@
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E4:K4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:K2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="E3:K3"/>
-    <mergeCell ref="E5:K5"/>
   </mergeCells>
   <pageMargins left="0.31388888888888899" right="0.31388888888888899" top="0.55000000000000004" bottom="0.55000000000000004" header="0.31388888888888899" footer="0.31388888888888899"/>
   <pageSetup paperSize="9" scale="57" fitToHeight="0" orientation="portrait" r:id="rId1"/>
